--- a/artfynd/A 20035-2024 artfynd.xlsx
+++ b/artfynd/A 20035-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1500,6 +1500,112 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126043623</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79127</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rönningsbergsån, Rönningsbergsån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>421685</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7051414</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lågproduktiv grannaturskog/sumpskog i högläge</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20035-2024 artfynd.xlsx
+++ b/artfynd/A 20035-2024 artfynd.xlsx
@@ -1505,7 +1505,7 @@
         <v>126043623</v>
       </c>
       <c r="B9" t="n">
-        <v>79127</v>
+        <v>79131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20035-2024 artfynd.xlsx
+++ b/artfynd/A 20035-2024 artfynd.xlsx
@@ -1505,7 +1505,7 @@
         <v>126043623</v>
       </c>
       <c r="B9" t="n">
-        <v>79131</v>
+        <v>79132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20035-2024 artfynd.xlsx
+++ b/artfynd/A 20035-2024 artfynd.xlsx
@@ -1505,7 +1505,7 @@
         <v>126043623</v>
       </c>
       <c r="B9" t="n">
-        <v>79132</v>
+        <v>79136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 20035-2024 artfynd.xlsx
+++ b/artfynd/A 20035-2024 artfynd.xlsx
@@ -1505,7 +1505,7 @@
         <v>126043623</v>
       </c>
       <c r="B9" t="n">
-        <v>79136</v>
+        <v>79139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
